--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484762_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484762_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2579</v>
+        <v>2.518</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7408</v>
+        <v>2.3712</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5172</v>
+        <v>0.1468</v>
       </c>
       <c r="G2" t="n">
         <v>1.039</v>
@@ -610,13 +610,13 @@
         <v>3.774</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2716</v>
+        <v>-1.0115</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4572</v>
+        <v>0.0876</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7288</v>
+        <v>-1.0992</v>
       </c>
       <c r="V2" t="n">
         <v>1.547</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ TORRES</t>
+          <t>N. FELIZ CAMEAU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6577</v>
+        <v>0.8548</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4753</v>
+        <v>1.248</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8175</v>
+        <v>-0.3932</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1476</v>
+        <v>-0.9253</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1496</v>
+        <v>0.8734</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.002</v>
+        <v>-1.7987</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0608</v>
+        <v>0.5749</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0197</v>
+        <v>1.1833</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0411</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0868</v>
+        <v>-1.5001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1299</v>
+        <v>-0.3099</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0431</v>
+        <v>-1.1902</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7548</v>
+        <v>1.887</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7548</v>
+        <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2833</v>
+        <v>-0.3897</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4144</v>
+        <v>-0.2323</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1311</v>
+        <v>-0.1575</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.528</v>
+        <v>0.2828</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.9054</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.528</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. FELIZ CAMEAU</t>
+          <t>J. DOMINGUEZ TORRES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5591</v>
+        <v>0.3125</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7407</v>
+        <v>1.1829</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1816</v>
+        <v>-0.8704</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9253</v>
+        <v>1.1476</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8734</v>
+        <v>1.1496</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7987</v>
+        <v>-0.002</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5749</v>
+        <v>1.0608</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1833</v>
+        <v>1.0197</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.0411</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5001</v>
+        <v>0.0868</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3099</v>
+        <v>0.1299</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1902</v>
+        <v>-0.0431</v>
       </c>
       <c r="P4" t="n">
-        <v>1.887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.887</v>
+        <v>0.7548</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6854</v>
+        <v>-0.0619</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7396</v>
+        <v>0.1221</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0542</v>
+        <v>-0.184</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2828</v>
+        <v>-1.528</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9054</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6226</v>
+        <v>-1.528</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8629</v>
+        <v>0.0308</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6591</v>
+        <v>-0.977</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7962</v>
+        <v>1.0078</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9994</v>
@@ -844,13 +844,13 @@
         <v>2.8305</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.0522</v>
+        <v>-1.1585</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9283</v>
+        <v>-0.2462</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1239</v>
+        <v>-0.9123</v>
       </c>
       <c r="V5" t="n">
         <v>1.2452</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0437</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4633</v>
+        <v>-0.1509</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5804</v>
+        <v>-0.4746</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1956</v>
@@ -922,13 +922,13 @@
         <v>2.0757</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2257</v>
+        <v>-0.8074</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.254</v>
+        <v>0.0584</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9717</v>
+        <v>-0.8658</v>
       </c>
       <c r="V6" t="n">
         <v>0.3018</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4824</v>
+        <v>-1.5164</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2318</v>
+        <v>-0.5039</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2506</v>
+        <v>-1.0125</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5832000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9365</v>
+        <v>-0.9705</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0152</v>
+        <v>-0.2569</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9517</v>
+        <v>-0.7136</v>
       </c>
       <c r="V7" t="n">
         <v>2.4904</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5594</v>
+        <v>-1.5329</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0165</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5429</v>
+        <v>-1.5164</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2019</v>
@@ -1078,13 +1078,13 @@
         <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.301</v>
+        <v>-0.2745</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2422</v>
+        <v>-0.2157</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2452</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1996</v>
+        <v>-2.0988</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2485</v>
+        <v>-3.9361</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0489</v>
+        <v>1.8373</v>
       </c>
       <c r="G9" t="n">
         <v>-3.3797</v>
@@ -1156,13 +1156,13 @@
         <v>3.5853</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1216</v>
+        <v>-1.0208</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6314</v>
+        <v>-0.319</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4902</v>
+        <v>-0.7018</v>
       </c>
       <c r="V9" t="n">
         <v>2.4904</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5724</v>
+        <v>-2.8479</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7268</v>
+        <v>-1.2139</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8456</v>
+        <v>-1.634</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6011</v>
@@ -1234,13 +1234,13 @@
         <v>1.1322</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1035</v>
+        <v>-0.379</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7359</v>
+        <v>0.2487</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8394</v>
+        <v>-0.6278</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.7604</v>
+        <v>-7.5126</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9266</v>
+        <v>-2.7318</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.8337</v>
+        <v>-4.7808</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9334</v>
@@ -1312,13 +1312,13 @@
         <v>2.2644</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0723</v>
+        <v>-0.8245</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2664</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.753</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1886</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.0061</v>
+        <v>-12.418</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.315799999999999</v>
+        <v>-4.728</v>
       </c>
       <c r="F12" t="n">
         <v>-7.69</v>
@@ -1357,13 +1357,13 @@
         <v>-13.633</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.620000000000001</v>
+        <v>-1.62</v>
       </c>
       <c r="I12" t="n">
         <v>-12.013</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.038499999999999</v>
+        <v>-1.0385</v>
       </c>
       <c r="K12" t="n">
         <v>3.185</v>
@@ -1390,13 +1390,13 @@
         <v>19.8135</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.4865</v>
+        <v>-6.898300000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2558</v>
+        <v>-0.6678999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.230700000000001</v>
+        <v>-6.2307</v>
       </c>
       <c r="V12" t="n">
         <v>3.395799999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.1572</v>
+        <v>10.7426</v>
       </c>
       <c r="E13" t="n">
-        <v>8.418699999999999</v>
+        <v>9.587899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7385</v>
+        <v>1.1547</v>
       </c>
       <c r="G13" t="n">
         <v>10.5888</v>
@@ -1468,13 +1468,13 @@
         <v>1.3209</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5637</v>
+        <v>1.0217</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.421</v>
+        <v>0.7483</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1427</v>
+        <v>0.2734</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3018</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. MEJIA ACOSTA</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5812</v>
+        <v>2.9936</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2356</v>
+        <v>-0.3531</v>
       </c>
       <c r="F14" t="n">
-        <v>4.8168</v>
+        <v>3.3467</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4764</v>
+        <v>1.0092</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4893</v>
+        <v>0.306</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9871</v>
+        <v>0.7032</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5416</v>
+        <v>0.5612</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4423</v>
+        <v>0.486</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0993</v>
+        <v>0.0752</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9348</v>
+        <v>0.448</v>
       </c>
       <c r="N14" t="n">
-        <v>0.047</v>
+        <v>-0.18</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8878</v>
+        <v>0.628</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.1514</v>
+        <v>1.3209</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.6045</v>
+        <v>-0.9435</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4531</v>
+        <v>2.2644</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7658</v>
+        <v>0.6635</v>
       </c>
       <c r="T14" t="n">
-        <v>2.035</v>
+        <v>0.0292</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7308</v>
+        <v>0.6343</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7922</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>G. MEJIA ACOSTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2424</v>
+        <v>2.8193</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8122</v>
+        <v>-1.3074</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4301</v>
+        <v>4.1267</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2703</v>
+        <v>2.4764</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0243</v>
+        <v>1.4893</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2946</v>
+        <v>0.9871</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3209</v>
+        <v>1.5416</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1683</v>
+        <v>1.4423</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4892</v>
+        <v>0.0993</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0506</v>
+        <v>0.9348</v>
       </c>
       <c r="N15" t="n">
-        <v>0.144</v>
+        <v>0.047</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1946</v>
+        <v>0.8878</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5661</v>
+        <v>-4.1514</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.887</v>
+        <v>-6.6045</v>
       </c>
       <c r="R15" t="n">
         <v>2.4531</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6512</v>
+        <v>2.0038</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3783</v>
+        <v>0.9633</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2728</v>
+        <v>1.0406</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2452</v>
+        <v>2.4904</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.7922</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8234</v>
+        <v>2.6351</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8403</v>
+        <v>1.9684</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6636</v>
+        <v>0.6667</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0092</v>
+        <v>1.5089</v>
       </c>
       <c r="H16" t="n">
-        <v>0.306</v>
+        <v>-1.6145</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7032</v>
+        <v>3.1234</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5612</v>
+        <v>1.0737</v>
       </c>
       <c r="K16" t="n">
-        <v>0.486</v>
+        <v>-0.4907</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0752</v>
+        <v>1.5644</v>
       </c>
       <c r="M16" t="n">
-        <v>0.448</v>
+        <v>0.4352</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.18</v>
+        <v>-1.1238</v>
       </c>
       <c r="O16" t="n">
-        <v>0.628</v>
+        <v>1.5589</v>
       </c>
       <c r="P16" t="n">
+        <v>-1.5096</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-2.8305</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.3209</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.9435</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.2644</v>
-      </c>
       <c r="S16" t="n">
-        <v>-0.5067</v>
+        <v>0.768</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.458</v>
+        <v>0.6122</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0488</v>
+        <v>0.1559</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.113</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6338</v>
+        <v>2.3799</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9069</v>
+        <v>0.7405</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2731</v>
+        <v>1.6394</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9903</v>
+        <v>1.2703</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3623</v>
+        <v>-0.0243</v>
       </c>
       <c r="I17" t="n">
-        <v>0.628</v>
+        <v>1.2946</v>
       </c>
       <c r="J17" t="n">
-        <v>1.442</v>
+        <v>1.3209</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0307</v>
+        <v>-0.1683</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4113</v>
+        <v>1.4892</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4516</v>
+        <v>-0.0506</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6683</v>
+        <v>0.144</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2167</v>
+        <v>-0.1946</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5661</v>
+        <v>2.4531</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6624</v>
+        <v>1.7887</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5031</v>
+        <v>1.3066</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1594</v>
+        <v>0.4821</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-1.2452</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9054</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.547</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>R. MOLLERMARK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5861</v>
+        <v>1.099</v>
       </c>
       <c r="E18" t="n">
-        <v>0.994</v>
+        <v>0.7817</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5921</v>
+        <v>0.3173</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5089</v>
+        <v>0.9176</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6145</v>
+        <v>1.1168</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1234</v>
+        <v>-0.1991</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0737</v>
+        <v>0.4524</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4907</v>
+        <v>1.0197</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5644</v>
+        <v>-0.5673</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4352</v>
+        <v>0.4652</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1238</v>
+        <v>0.097</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5589</v>
+        <v>0.3682</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3209</v>
+        <v>0.9435</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2809</v>
+        <v>0.7849</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3622</v>
+        <v>0.3293</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.4556</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8678</v>
+        <v>-1.547</v>
       </c>
       <c r="W18" t="n">
-        <v>3.113</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2452</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9339</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9339</v>
+        <v>2.2249</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-1.2249</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9339</v>
+        <v>0.9903</v>
       </c>
       <c r="H19" t="n">
-        <v>0.317</v>
+        <v>0.3623</v>
       </c>
       <c r="I19" t="n">
-        <v>0.617</v>
+        <v>0.628</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9339</v>
+        <v>1.442</v>
       </c>
       <c r="K19" t="n">
-        <v>0.317</v>
+        <v>1.0307</v>
       </c>
       <c r="L19" t="n">
-        <v>0.617</v>
+        <v>0.4113</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.4516</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.6683</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.2167</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.0286</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.821</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2076</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.9054</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. MOLLERMARK</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8285</v>
+        <v>0.9339</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8792</v>
+        <v>0.9339</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0507</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9176</v>
+        <v>0.9339</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1168</v>
+        <v>0.317</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1991</v>
+        <v>0.617</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4524</v>
+        <v>0.9339</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0197</v>
+        <v>0.317</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5673</v>
+        <v>0.617</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4652</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3682</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5143</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4267</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0876</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. ZOROA GARCIA</t>
+          <t>B. MALONE NAVARRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4672</v>
+        <v>-1.4936</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2727</v>
+        <v>-2.4732</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1945</v>
+        <v>0.9796</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002</v>
+        <v>-2.3295</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.299</v>
+        <v>-0.7489</v>
       </c>
       <c r="I21" t="n">
-        <v>0.301</v>
+        <v>-1.5805</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0677</v>
+        <v>-1.8853</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0266</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0411</v>
+        <v>-1.2991</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.4442</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3256</v>
+        <v>-0.1628</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2598</v>
+        <v>-0.2814</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5308</v>
+        <v>0.4585</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6031</v>
+        <v>0.3556</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0723</v>
+        <v>0.1029</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. MALONE NAVARRO</t>
+          <t>E. ZOROA GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.52</v>
+        <v>-1.7149</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4732</v>
+        <v>-0.4675</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9532</v>
+        <v>-1.2474</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3295</v>
+        <v>0.002</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7489</v>
+        <v>-0.299</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5805</v>
+        <v>0.301</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8853</v>
+        <v>0.0677</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.0266</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2991</v>
+        <v>0.0411</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4442</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1628</v>
+        <v>-0.3256</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2814</v>
+        <v>0.2598</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3774</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="S22" t="n">
-        <v>0.432</v>
+        <v>0.283</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3556</v>
+        <v>0.4082</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0764</v>
+        <v>-0.1252</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8993</v>
+        <v>-2.0297</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.228</v>
+        <v>-2.9357</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3287</v>
+        <v>0.906</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4417</v>
@@ -2248,13 +2248,13 @@
         <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2122</v>
+        <v>0.6574</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2627</v>
+        <v>0.555</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4749</v>
+        <v>0.1023</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8941</v>
+        <v>-4.4106</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2052</v>
+        <v>-1.0104</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6889</v>
+        <v>-3.4002</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2934</v>
@@ -2326,13 +2326,13 @@
         <v>0.3774</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5067</v>
+        <v>-0.0232</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0929</v>
+        <v>0.102</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4138</v>
+        <v>-0.1252</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4714</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>13.0059</v>
+        <v>14.9546</v>
       </c>
       <c r="E25" t="n">
-        <v>7.6899</v>
+        <v>7.689999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>5.315800000000001</v>
+        <v>7.264599999999998</v>
       </c>
       <c r="G25" t="n">
         <v>13.6328</v>
@@ -2383,7 +2383,7 @@
         <v>4.805</v>
       </c>
       <c r="L25" t="n">
-        <v>7.789499999999999</v>
+        <v>7.789500000000001</v>
       </c>
       <c r="M25" t="n">
         <v>1.0385</v>
@@ -2404,13 +2404,13 @@
         <v>15.096</v>
       </c>
       <c r="S25" t="n">
-        <v>7.486300000000001</v>
+        <v>9.434900000000003</v>
       </c>
       <c r="T25" t="n">
-        <v>6.230399999999999</v>
+        <v>6.2307</v>
       </c>
       <c r="U25" t="n">
-        <v>1.2557</v>
+        <v>3.204299999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-3.3958</v>
